--- a/Transcendence.xlsx
+++ b/Transcendence.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\David\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{217947B4-7F61-4214-980F-3974C3F29D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17870F87-3DA9-49DB-BC64-46B7980B2E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FA75B51-8827-433F-B8D9-AFD99CF66ECC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2FA75B51-8827-433F-B8D9-AFD99CF66ECC}"/>
   </bookViews>
   <sheets>
     <sheet name="Modulos" sheetId="1" r:id="rId1"/>
     <sheet name="Tabla dinamica" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Modulos!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Modulos!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="42" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,10 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
-  <si>
-    <t>Quizá</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="53">
   <si>
     <t>Web</t>
   </si>
@@ -196,7 +193,13 @@
     <t>Carlos y Claudia</t>
   </si>
   <si>
-    <t>Viernes</t>
+    <t>Quiza</t>
+  </si>
+  <si>
+    <t>Belmiro</t>
+  </si>
+  <si>
+    <t>Bonus</t>
   </si>
 </sst>
 </file>
@@ -232,17 +235,294 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="38">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -256,13 +536,24 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="David" refreshedDate="45707.793034374998" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{D46246A2-85E3-4FFF-8847-8F5AAA9AD5B3}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="David" refreshedDate="45709.586138194441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{D46246A2-85E3-4FFF-8847-8F5AAA9AD5B3}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:E1048576" sheet="Modulos"/>
   </cacheSource>
   <cacheFields count="5">
     <cacheField name="Tipo" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems containsBlank="1" count="10">
+        <s v="Web"/>
+        <s v="User Management"/>
+        <s v="Gameplay and UX"/>
+        <s v="AI - Algo"/>
+        <s v="Cyber"/>
+        <s v="Devops"/>
+        <s v="Graphics"/>
+        <s v="Accessibility"/>
+        <s v="Server-Side Pong"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Desc" numFmtId="0">
       <sharedItems containsBlank="1" count="28">
@@ -303,13 +594,15 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Elección" numFmtId="0">
-      <sharedItems containsBlank="1" count="6">
+      <sharedItems containsBlank="1" count="8">
         <s v="Seguro"/>
-        <s v="Viernes"/>
+        <s v="Bonus"/>
         <s v="No"/>
-        <s v="Quizá"/>
         <m/>
+        <s v="Viernes" u="1"/>
+        <s v="Quiza" u="1"/>
         <s v="Si" u="1"/>
+        <s v="Quizá" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -324,209 +617,223 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="28">
   <r>
-    <s v="Web"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Done"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Web"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="0.5"/>
     <s v="Done"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Web"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="0.5"/>
     <s v="Done"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Web"/>
+    <x v="0"/>
     <x v="3"/>
-    <n v="0.5"/>
+    <n v="1"/>
     <s v="David"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="User Management"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="User Management"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="1"/>
     <s v="Carlos"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Gameplay and UX"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="Gameplay and UX"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="1"/>
     <s v="Claudia"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Gameplay and UX"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="Gameplay and UX"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="0.5"/>
     <s v="Claudia"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Gameplay and UX"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="AI - Algo"/>
+    <x v="3"/>
     <x v="11"/>
     <n v="1"/>
     <s v="Carlos y Claudia"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="AI - Algo"/>
+    <x v="3"/>
     <x v="12"/>
     <n v="0.5"/>
     <s v="David"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="Cyber"/>
+    <x v="4"/>
     <x v="13"/>
     <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="Cyber"/>
+    <x v="4"/>
     <x v="14"/>
     <n v="0.5"/>
     <s v="David"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="Cyber"/>
+    <x v="4"/>
     <x v="15"/>
     <n v="1"/>
     <s v="Carlos"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="Devops"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
     <x v="16"/>
     <n v="1"/>
     <s v="David"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <s v="Devops"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
     <x v="17"/>
     <n v="0.5"/>
     <s v="David"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <s v="Devops"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
     <x v="18"/>
     <n v="1"/>
     <s v="David"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <s v="Graphics"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="6"/>
     <x v="19"/>
     <n v="1"/>
     <s v="Carlos"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="Accessibility"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
     <x v="20"/>
     <n v="0.5"/>
     <s v="Done"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Accessibility"/>
+    <x v="7"/>
     <x v="21"/>
     <n v="0.5"/>
     <s v="Done"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Accessibility"/>
+    <x v="7"/>
     <x v="22"/>
     <n v="0.5"/>
     <s v="Claudia"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="Accessibility"/>
+    <x v="7"/>
     <x v="23"/>
     <n v="0.5"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="Accessibility"/>
+    <x v="7"/>
     <x v="24"/>
     <n v="0.5"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="Server-Side Pong"/>
+    <x v="8"/>
     <x v="25"/>
     <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <s v="Server-Side Pong"/>
+    <x v="8"/>
     <x v="26"/>
-    <n v="0.5"/>
+    <n v="1"/>
     <m/>
     <x v="2"/>
   </r>
   <r>
-    <m/>
+    <x v="9"/>
     <x v="27"/>
     <m/>
     <m/>
-    <x v="4"/>
+    <x v="3"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{99958509-F436-4D67-8804-4E5B06CBF099}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{99958509-F436-4D67-8804-4E5B06CBF099}" name="TablaDinámica2" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="7"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="29">
         <item x="23"/>
@@ -562,36 +869,76 @@
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="7">
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="9">
         <item h="1" x="2"/>
+        <item m="1" x="7"/>
+        <item m="1" x="6"/>
         <item h="1" x="3"/>
+        <item x="0"/>
+        <item m="1" x="4"/>
         <item m="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
+        <item sd="0" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="3">
+    <field x="4"/>
+    <field x="0"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="18">
     <i>
-      <x v="6"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i r="2">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
     </i>
     <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
+      <x v="7"/>
     </i>
     <i t="grand">
       <x/>
@@ -600,12 +947,122 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
   <dataFields count="1">
     <dataField name="Suma de Tipo2" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="7">
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="5">
+            <x v="2"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="7"/>
+            <x v="8"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="3">
+            <x v="4"/>
+            <x v="15"/>
+            <x v="21"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1">
+            <x v="7"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="2">
+            <x v="5"/>
+            <x v="14"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="1">
+            <x v="25"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1">
+            <x v="9"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="3">
+            <x v="22"/>
+            <x v="23"/>
+            <x v="24"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -915,547 +1372,671 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584E36CC-E709-4435-B8B5-67790CA2252D}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>45</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0.5</v>
       </c>
       <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>46</v>
       </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
       </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
       </c>
       <c r="C11">
         <v>0.5</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
         <v>19</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
       </c>
       <c r="C14">
         <v>0.5</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
         <v>21</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
       </c>
       <c r="C16">
         <v>0.5</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>24</v>
       </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
         <v>26</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
       </c>
       <c r="C19">
         <v>0.5</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
         <v>28</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>31</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
       </c>
       <c r="C22">
         <v>0.5</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>0.5</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>0.5</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>0.5</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>0.5</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
         <v>37</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
         <v>38</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>39</v>
       </c>
-      <c r="C28">
-        <v>0.5</v>
-      </c>
-      <c r="E28" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E28" xr:uid="{584E36CC-E709-4435-B8B5-67790CA2252D}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Viernes"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F28" xr:uid="{584E36CC-E709-4435-B8B5-67790CA2252D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28B2B21-4DA2-4890-BA79-5946EB13D2A7}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A3:B21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="84.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>51</v>
-      </c>
-    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
         <v>41</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="4">
         <v>11</v>
-      </c>
-      <c r="B6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9">
-        <v>3.5</v>
       </c>
     </row>
   </sheetData>
